--- a/result/R110_Test.xlsx
+++ b/result/R110_Test.xlsx
@@ -452,13 +452,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="3">
-        <v>1231.36</v>
+        <v>1209.79</v>
       </c>
       <c r="D4" s="3">
-        <v>1231.36</v>
+        <v>1209.79</v>
       </c>
       <c r="E4" s="3">
-        <v>89.76000000000001</v>
+        <v>125.46</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -469,13 +469,13 @@
         <v>12</v>
       </c>
       <c r="C5" s="3">
-        <v>1231.36</v>
+        <v>1209.79</v>
       </c>
       <c r="D5" s="3">
-        <v>1231.36</v>
+        <v>1209.79</v>
       </c>
       <c r="E5" s="3">
-        <v>89.76000000000001</v>
+        <v>125.46</v>
       </c>
     </row>
   </sheetData>
